--- a/Result/profitability/1785.xlsx
+++ b/Result/profitability/1785.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.45</v>
+        <v>1.4925</v>
       </c>
       <c r="N2" t="n">
-        <v>14.24</v>
+        <v>13.73</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.55125</v>
+        <v>1.55375</v>
       </c>
       <c r="N3" t="n">
-        <v>14.23875</v>
+        <v>14.085</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5975</v>
+        <v>1.66125</v>
       </c>
       <c r="N4" t="n">
-        <v>14.9275</v>
+        <v>14.30375</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.22</v>
+        <v>1.42125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.1875</v>
+        <v>10.79875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.31875</v>
+        <v>1.31125</v>
       </c>
       <c r="N6" t="n">
-        <v>10.68125</v>
+        <v>10.1375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>1.39</v>
+        <v>1.295</v>
       </c>
       <c r="N7" t="n">
-        <v>10.1725</v>
+        <v>9.286250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>1.09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2925</v>
+        <v>1.11375</v>
       </c>
       <c r="N8" t="n">
-        <v>9.088749999999999</v>
+        <v>8.0275</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.93125</v>
       </c>
       <c r="N10" t="n">
-        <v>7.391249999999999</v>
+        <v>7.39125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9339,13 +9339,13 @@
         <v>9525</v>
       </c>
       <c r="D71" t="n">
-        <v>8361</v>
+        <v>8295</v>
       </c>
       <c r="E71" t="n">
-        <v>1163</v>
+        <v>1229</v>
       </c>
       <c r="F71" t="n">
-        <v>12.22</v>
+        <v>12.91</v>
       </c>
       <c r="G71" t="n">
         <v>1008</v>
@@ -9371,7 +9371,7 @@
         <v>0.5125</v>
       </c>
       <c r="N71" t="n">
-        <v>12.88625</v>
+        <v>12.9725</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9404,10 +9404,10 @@
         <v>-1.833333333333333</v>
       </c>
       <c r="Y71" t="n">
-        <v>-2.569999999999999</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="Z71" t="n">
-        <v>-0.1737660581473968</v>
+        <v>-0.1271129141311697</v>
       </c>
       <c r="AA71" t="n">
         <v>-1.12</v>
@@ -9416,10 +9416,10 @@
         <v>-1.806451612903226</v>
       </c>
       <c r="AC71" t="n">
-        <v>-2.68</v>
+        <v>-1.99</v>
       </c>
       <c r="AD71" t="n">
-        <v>-0.1798657718120805</v>
+        <v>-0.1335570469798658</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9466,13 +9466,13 @@
         <v>10435</v>
       </c>
       <c r="D72" t="n">
-        <v>8965</v>
+        <v>9031</v>
       </c>
       <c r="E72" t="n">
-        <v>1470</v>
+        <v>1404</v>
       </c>
       <c r="F72" t="n">
-        <v>14.09</v>
+        <v>13.46</v>
       </c>
       <c r="G72" t="n">
         <v>959</v>
@@ -9498,7 +9498,7 @@
         <v>0.5725</v>
       </c>
       <c r="N72" t="n">
-        <v>13.125</v>
+        <v>13.1325</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9531,10 +9531,10 @@
         <v>-3.34</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.869999999999999</v>
+        <v>0.5500000000000007</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.1530278232405891</v>
+        <v>0.04260263361735084</v>
       </c>
       <c r="AA72" t="n">
         <v>0.3999999999999999</v>
@@ -9543,10 +9543,10 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.2099999999999991</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.01512968299711814</v>
+        <v>-0.03025936599423629</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9558,14 +9558,14 @@
         <v>1</v>
       </c>
       <c r="AH72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率成長</t>
+          <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9625,7 +9625,7 @@
         <v>0.7937500000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>13.6325</v>
+        <v>13.64</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -9658,10 +9658,10 @@
         <v>0.5982905982905984</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.739999999999998</v>
+        <v>3.369999999999997</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.1944641589779985</v>
+        <v>0.2503714710252598</v>
       </c>
       <c r="AA73" t="n">
         <v>0.78</v>
@@ -9752,7 +9752,7 @@
         <v>1.02</v>
       </c>
       <c r="N74" t="n">
-        <v>14.49625</v>
+        <v>14.50375</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>15685</v>
+      </c>
+      <c r="D75" t="n">
+        <v>14157</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1528</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1098</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-186</v>
+      </c>
+      <c r="J75" t="n">
+        <v>913</v>
+      </c>
+      <c r="K75" t="n">
+        <v>662</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.08125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.85875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5629921259842519</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4657158529895776</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2455460883036406</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
